--- a/script/Datos_IO.xlsx
+++ b/script/Datos_IO.xlsx
@@ -3950,8 +3950,8 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Documento" ma:contentTypeID="0x010100B280F585ACC6394D940A341890B29E43" ma:contentTypeVersion="13" ma:contentTypeDescription="Crear nuevo documento." ma:contentTypeScope="" ma:versionID="0d5d610ba77d89fa1ad7fd005905942e">
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="7a056484-224d-44b1-98a6-1e28755ac544" xmlns:ns3="a85a52da-888d-44f6-a876-043783891b0c" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="2f2308da207518e82daff8d4f0944dd0" ns2:_="" ns3:_="">
+<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100B280F585ACC6394D940A341890B29E43" ma:contentTypeVersion="13" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="d1f1fcebf4b6756f6d1fc9d9c3b3fa3b">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="7a056484-224d-44b1-98a6-1e28755ac544" xmlns:ns3="a85a52da-888d-44f6-a876-043783891b0c" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="4b3f257e48ff9960a0b3d6bd1a4158eb" ns2:_="" ns3:_="">
     <xsd:import namespace="7a056484-224d-44b1-98a6-1e28755ac544"/>
     <xsd:import namespace="a85a52da-888d-44f6-a876-043783891b0c"/>
     <xsd:element name="properties">
@@ -4002,7 +4002,7 @@
         <xsd:restriction base="dms:Text"/>
       </xsd:simpleType>
     </xsd:element>
-    <xsd:element name="lcf76f155ced4ddcb4097134ff3c332f" ma:index="13" nillable="true" ma:taxonomy="true" ma:internalName="lcf76f155ced4ddcb4097134ff3c332f" ma:taxonomyFieldName="MediaServiceImageTags" ma:displayName="Etiquetas de imagen" ma:readOnly="false" ma:fieldId="{5cf76f15-5ced-4ddc-b409-7134ff3c332f}" ma:taxonomyMulti="true" ma:sspId="86e00edd-d097-4c46-a7a4-3c3000150473" ma:termSetId="09814cd3-568e-fe90-9814-8d621ff8fb84" ma:anchorId="fba54fb3-c3e1-fe81-a776-ca4b69148c4d" ma:open="true" ma:isKeyword="false">
+    <xsd:element name="lcf76f155ced4ddcb4097134ff3c332f" ma:index="13" nillable="true" ma:taxonomy="true" ma:internalName="lcf76f155ced4ddcb4097134ff3c332f" ma:taxonomyFieldName="MediaServiceImageTags" ma:displayName="Image Tags" ma:readOnly="false" ma:fieldId="{5cf76f15-5ced-4ddc-b409-7134ff3c332f}" ma:taxonomyMulti="true" ma:sspId="86e00edd-d097-4c46-a7a4-3c3000150473" ma:termSetId="09814cd3-568e-fe90-9814-8d621ff8fb84" ma:anchorId="fba54fb3-c3e1-fe81-a776-ca4b69148c4d" ma:open="true" ma:isKeyword="false">
       <xsd:complexType>
         <xsd:sequence>
           <xsd:element ref="pc:Terms" minOccurs="0" maxOccurs="1"/>
@@ -4066,8 +4066,8 @@
         <xsd:element ref="dc:creator" minOccurs="0" maxOccurs="1"/>
         <xsd:element ref="dcterms:created" minOccurs="0" maxOccurs="1"/>
         <xsd:element ref="dc:identifier" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Tipo de contenido"/>
-        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Título"/>
+        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Content Type"/>
+        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Title"/>
         <xsd:element ref="dc:subject" minOccurs="0" maxOccurs="1"/>
         <xsd:element ref="dc:description" minOccurs="0" maxOccurs="1"/>
         <xsd:element name="keywords" minOccurs="0" maxOccurs="1" type="xsd:string"/>
@@ -4177,22 +4177,7 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C70B5468-74D4-467B-8BFF-B704E11604A0}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="7a056484-224d-44b1-98a6-1e28755ac544"/>
-    <ds:schemaRef ds:uri="a85a52da-888d-44f6-a876-043783891b0c"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8BDF1938-957A-4B80-90BF-5F088B30A6C3}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
